--- a/db/data/office_transactions.xlsx
+++ b/db/data/office_transactions.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22624"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\storemgmt\db\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004DB22F-C754-4190-9451-60869542A4FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -856,8 +857,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,9 +1227,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M375"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
@@ -1246,7 +1247,7 @@
     <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>242</v>
       </c>
@@ -1287,7 +1288,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1318,7 +1319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1357,7 +1358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1392,7 +1393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1423,7 +1424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1446,7 +1447,7 @@
       </c>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1473,7 +1474,7 @@
       </c>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1502,7 +1503,7 @@
       </c>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1529,7 +1530,7 @@
       </c>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1556,7 +1557,7 @@
       </c>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>6</v>
       </c>
@@ -1581,7 +1582,7 @@
       </c>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>6</v>
       </c>
@@ -1610,7 +1611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>7</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>7</v>
       </c>
@@ -1664,7 +1665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>8</v>
       </c>
@@ -1691,7 +1692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>8</v>
       </c>
@@ -1722,7 +1723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>8</v>
       </c>
@@ -1753,7 +1754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1784,7 +1785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>8</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>8</v>
       </c>
@@ -1846,7 +1847,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>8</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>8</v>
       </c>
@@ -1908,7 +1909,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>8</v>
       </c>
@@ -1939,7 +1940,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13">
       <c r="A24">
         <v>8</v>
       </c>
@@ -1970,7 +1971,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13">
       <c r="A25">
         <v>9</v>
       </c>
@@ -1999,7 +2000,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13">
       <c r="A26">
         <v>10</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2078,7 +2079,7 @@
       </c>
       <c r="M28"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13">
       <c r="A29">
         <v>10</v>
       </c>
@@ -2107,7 +2108,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13">
       <c r="A30">
         <v>11</v>
       </c>
@@ -2134,7 +2135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13">
       <c r="A31">
         <v>11</v>
       </c>
@@ -2161,7 +2162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13">
       <c r="A32">
         <v>11</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13">
       <c r="A33">
         <v>11</v>
       </c>
@@ -2217,7 +2218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13">
       <c r="A34">
         <v>12</v>
       </c>
@@ -2242,7 +2243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13">
       <c r="A35">
         <v>13</v>
       </c>
@@ -2267,7 +2268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13">
       <c r="A36">
         <v>14</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13">
       <c r="A37">
         <v>15</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13">
       <c r="A38">
         <v>16</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13">
       <c r="A39">
         <v>17</v>
       </c>
@@ -2367,7 +2368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13">
       <c r="A40">
         <v>18</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13">
       <c r="A41">
         <v>19</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13">
       <c r="A42">
         <v>19</v>
       </c>
@@ -2444,7 +2445,7 @@
       </c>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13">
       <c r="A43">
         <v>20</v>
       </c>
@@ -2469,7 +2470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13">
       <c r="A44">
         <v>20</v>
       </c>
@@ -2494,7 +2495,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13">
       <c r="A45">
         <v>21</v>
       </c>
@@ -2519,7 +2520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13">
       <c r="A46">
         <v>22</v>
       </c>
@@ -2544,7 +2545,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13">
       <c r="A47">
         <v>23</v>
       </c>
@@ -2569,7 +2570,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13">
       <c r="A48">
         <v>24</v>
       </c>
@@ -2594,7 +2595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13">
       <c r="A49">
         <v>25</v>
       </c>
@@ -2619,7 +2620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13">
       <c r="A50">
         <v>25</v>
       </c>
@@ -2644,7 +2645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13">
       <c r="A51">
         <v>26</v>
       </c>
@@ -2669,7 +2670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13">
       <c r="A52">
         <v>26</v>
       </c>
@@ -2694,7 +2695,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13">
       <c r="A53">
         <v>26</v>
       </c>
@@ -2719,7 +2720,7 @@
       </c>
       <c r="M53"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13">
       <c r="A54">
         <v>27</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13">
       <c r="A55">
         <v>28</v>
       </c>
@@ -2769,7 +2770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13">
       <c r="A56">
         <v>29</v>
       </c>
@@ -2794,7 +2795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13">
       <c r="A57">
         <v>29</v>
       </c>
@@ -2819,7 +2820,7 @@
       </c>
       <c r="M57"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13">
       <c r="A58">
         <v>29</v>
       </c>
@@ -2844,7 +2845,7 @@
       </c>
       <c r="M58"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13">
       <c r="A59">
         <v>29</v>
       </c>
@@ -2869,7 +2870,7 @@
       </c>
       <c r="M59"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13">
       <c r="A60">
         <v>29</v>
       </c>
@@ -2894,7 +2895,7 @@
       </c>
       <c r="M60"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13">
       <c r="A61">
         <v>29</v>
       </c>
@@ -2919,7 +2920,7 @@
       </c>
       <c r="M61"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13">
       <c r="A62">
         <v>29</v>
       </c>
@@ -2944,7 +2945,7 @@
       </c>
       <c r="M62"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13">
       <c r="A63">
         <v>29</v>
       </c>
@@ -2969,7 +2970,7 @@
       </c>
       <c r="M63"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13">
       <c r="A64">
         <v>29</v>
       </c>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="M64"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13">
       <c r="A65">
         <v>29</v>
       </c>
@@ -3019,7 +3020,7 @@
       </c>
       <c r="M65"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13">
       <c r="A66">
         <v>30</v>
       </c>
@@ -3042,7 +3043,7 @@
       </c>
       <c r="M66"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13">
       <c r="A67">
         <v>31</v>
       </c>
@@ -3067,7 +3068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13">
       <c r="A68">
         <v>32</v>
       </c>
@@ -3092,7 +3093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13">
       <c r="A69">
         <v>33</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13">
       <c r="A70">
         <v>44</v>
       </c>
@@ -3142,7 +3143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13">
       <c r="A71">
         <v>44</v>
       </c>
@@ -3167,7 +3168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13">
       <c r="A72">
         <v>44</v>
       </c>
@@ -3192,7 +3193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13">
       <c r="A73">
         <v>35</v>
       </c>
@@ -3217,7 +3218,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13">
       <c r="A74">
         <v>35</v>
       </c>
@@ -3242,7 +3243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13">
       <c r="A75">
         <v>35</v>
       </c>
@@ -3267,7 +3268,7 @@
       </c>
       <c r="M75"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13">
       <c r="A76">
         <v>35</v>
       </c>
@@ -3290,7 +3291,7 @@
       </c>
       <c r="M76"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13">
       <c r="A77">
         <v>36</v>
       </c>
@@ -3315,7 +3316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13">
       <c r="A78">
         <v>37</v>
       </c>
@@ -3340,7 +3341,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13">
       <c r="A79">
         <v>38</v>
       </c>
@@ -3365,7 +3366,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13">
       <c r="A80">
         <v>39</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13">
       <c r="A81">
         <v>40</v>
       </c>
@@ -3415,7 +3416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13">
       <c r="A82">
         <v>41</v>
       </c>
@@ -3440,7 +3441,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13">
       <c r="A83">
         <v>42</v>
       </c>
@@ -3465,7 +3466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13">
       <c r="A84">
         <v>43</v>
       </c>
@@ -3490,7 +3491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13">
       <c r="A85">
         <v>44</v>
       </c>
@@ -3515,7 +3516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13">
       <c r="A86">
         <v>45</v>
       </c>
@@ -3540,7 +3541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13">
       <c r="A87">
         <v>45</v>
       </c>
@@ -3565,7 +3566,7 @@
       </c>
       <c r="M87"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13">
       <c r="A88">
         <v>45</v>
       </c>
@@ -3590,7 +3591,7 @@
       </c>
       <c r="M88"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13">
       <c r="A89">
         <v>46</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13">
       <c r="A90">
         <v>47</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13">
       <c r="A91">
         <v>47</v>
       </c>
@@ -3663,7 +3664,7 @@
       </c>
       <c r="M91"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13">
       <c r="A92">
         <v>48</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13">
       <c r="A93">
         <v>49</v>
       </c>
@@ -3713,7 +3714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13">
       <c r="A94">
         <v>49</v>
       </c>
@@ -3740,7 +3741,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13">
       <c r="A95">
         <v>49</v>
       </c>
@@ -3765,7 +3766,7 @@
       </c>
       <c r="M95"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13">
       <c r="A96">
         <v>49</v>
       </c>
@@ -3790,7 +3791,7 @@
       </c>
       <c r="M96"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13">
       <c r="A97">
         <v>49</v>
       </c>
@@ -3815,7 +3816,7 @@
       </c>
       <c r="M97"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13">
       <c r="A98">
         <v>50</v>
       </c>
@@ -3842,7 +3843,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13">
       <c r="A99">
         <v>50</v>
       </c>
@@ -3869,7 +3870,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13">
       <c r="A100">
         <v>50</v>
       </c>
@@ -3896,7 +3897,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13">
       <c r="A101">
         <v>50</v>
       </c>
@@ -3925,7 +3926,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13">
       <c r="A102">
         <v>50</v>
       </c>
@@ -3954,7 +3955,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13">
       <c r="A103">
         <v>50</v>
       </c>
@@ -3981,7 +3982,7 @@
       </c>
       <c r="M103"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13">
       <c r="A104">
         <v>50</v>
       </c>
@@ -4010,7 +4011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13">
       <c r="A105">
         <v>50</v>
       </c>
@@ -4039,7 +4040,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13">
       <c r="A106">
         <v>50</v>
       </c>
@@ -4068,7 +4069,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13">
       <c r="A107">
         <v>50</v>
       </c>
@@ -4097,7 +4098,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13">
       <c r="A108">
         <v>50</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13">
       <c r="A109">
         <v>50</v>
       </c>
@@ -4155,7 +4156,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13">
       <c r="A110">
         <v>50</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13">
       <c r="A111">
         <v>50</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13">
       <c r="A112">
         <v>51</v>
       </c>
@@ -4238,7 +4239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13">
       <c r="A113">
         <v>51</v>
       </c>
@@ -4263,7 +4264,7 @@
       </c>
       <c r="M113"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13">
       <c r="A114">
         <v>52</v>
       </c>
@@ -4288,7 +4289,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13">
       <c r="A115">
         <v>53</v>
       </c>
@@ -4313,7 +4314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13">
       <c r="A116">
         <v>53</v>
       </c>
@@ -4338,7 +4339,7 @@
       </c>
       <c r="M116"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13">
       <c r="A117">
         <v>54</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13">
       <c r="A118">
         <v>55</v>
       </c>
@@ -4388,7 +4389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13">
       <c r="A119">
         <v>55</v>
       </c>
@@ -4415,7 +4416,7 @@
       </c>
       <c r="M119"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13">
       <c r="A120">
         <v>56</v>
       </c>
@@ -4440,7 +4441,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13">
       <c r="A121">
         <v>57</v>
       </c>
@@ -4465,7 +4466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13">
       <c r="A122">
         <v>58</v>
       </c>
@@ -4490,7 +4491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13">
       <c r="A123">
         <v>59</v>
       </c>
@@ -4515,7 +4516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13">
       <c r="A124">
         <v>60</v>
       </c>
@@ -4540,7 +4541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13">
       <c r="A125">
         <v>61</v>
       </c>
@@ -4565,7 +4566,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13">
       <c r="A126">
         <v>62</v>
       </c>
@@ -4590,7 +4591,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13">
       <c r="A127">
         <v>63</v>
       </c>
@@ -4615,7 +4616,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13">
       <c r="A128">
         <v>64</v>
       </c>
@@ -4640,7 +4641,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13">
       <c r="A129">
         <v>65</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13">
       <c r="A130">
         <v>66</v>
       </c>
@@ -4690,7 +4691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13">
       <c r="A131">
         <v>66</v>
       </c>
@@ -4717,7 +4718,7 @@
       </c>
       <c r="M131"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13">
       <c r="A132">
         <v>67</v>
       </c>
@@ -4742,7 +4743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13">
       <c r="A133">
         <v>67</v>
       </c>
@@ -4769,7 +4770,7 @@
       </c>
       <c r="M133"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13">
       <c r="A134">
         <v>67</v>
       </c>
@@ -4794,7 +4795,7 @@
       </c>
       <c r="M134"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13">
       <c r="A135">
         <v>68</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13">
       <c r="A136">
         <v>68</v>
       </c>
@@ -4844,7 +4845,7 @@
       </c>
       <c r="M136"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13">
       <c r="A137">
         <v>68</v>
       </c>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="M137"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13">
       <c r="A138">
         <v>69</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13">
       <c r="A139">
         <v>70</v>
       </c>
@@ -4921,7 +4922,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13">
       <c r="A140">
         <v>70</v>
       </c>
@@ -4946,7 +4947,7 @@
       </c>
       <c r="M140"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13">
       <c r="A141">
         <v>71</v>
       </c>
@@ -4971,7 +4972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13">
       <c r="A142">
         <v>72</v>
       </c>
@@ -4996,7 +4997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13">
       <c r="A143">
         <v>73</v>
       </c>
@@ -5021,7 +5022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13">
       <c r="A144">
         <v>74</v>
       </c>
@@ -5046,7 +5047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13">
       <c r="A145">
         <v>76</v>
       </c>
@@ -5071,7 +5072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13">
       <c r="A146">
         <v>76</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13">
       <c r="A147">
         <v>76</v>
       </c>
@@ -5121,7 +5122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13">
       <c r="A148">
         <v>76</v>
       </c>
@@ -5144,7 +5145,7 @@
       </c>
       <c r="M148"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13">
       <c r="A149">
         <v>77</v>
       </c>
@@ -5169,7 +5170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13">
       <c r="A150">
         <v>77</v>
       </c>
@@ -5194,7 +5195,7 @@
       </c>
       <c r="M150"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13">
       <c r="A151">
         <v>77</v>
       </c>
@@ -5219,7 +5220,7 @@
       </c>
       <c r="M151"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13">
       <c r="A152">
         <v>77</v>
       </c>
@@ -5244,7 +5245,7 @@
       </c>
       <c r="M152"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13">
       <c r="A153">
         <v>77</v>
       </c>
@@ -5269,7 +5270,7 @@
       </c>
       <c r="M153"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13">
       <c r="A154">
         <v>78</v>
       </c>
@@ -5294,7 +5295,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13">
       <c r="A155">
         <v>78</v>
       </c>
@@ -5319,7 +5320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13">
       <c r="A156">
         <v>78</v>
       </c>
@@ -5344,7 +5345,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13">
       <c r="A157">
         <v>78</v>
       </c>
@@ -5367,7 +5368,7 @@
       </c>
       <c r="M157"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13">
       <c r="A158">
         <v>78</v>
       </c>
@@ -5390,7 +5391,7 @@
       </c>
       <c r="M158"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13">
       <c r="A159">
         <v>78</v>
       </c>
@@ -5415,7 +5416,7 @@
       </c>
       <c r="M159"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13">
       <c r="A160">
         <v>78</v>
       </c>
@@ -5440,7 +5441,7 @@
       </c>
       <c r="M160"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13">
       <c r="A161">
         <v>79</v>
       </c>
@@ -5465,7 +5466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13">
       <c r="A162">
         <v>80</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13">
       <c r="A163">
         <v>85</v>
       </c>
@@ -5515,7 +5516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13">
       <c r="A164">
         <v>85</v>
       </c>
@@ -5540,7 +5541,7 @@
       </c>
       <c r="M164"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13">
       <c r="A165">
         <v>87</v>
       </c>
@@ -5565,7 +5566,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13">
       <c r="A166">
         <v>87</v>
       </c>
@@ -5588,7 +5589,7 @@
       </c>
       <c r="M166"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13">
       <c r="A167">
         <v>88</v>
       </c>
@@ -5613,7 +5614,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13">
       <c r="A168">
         <v>88</v>
       </c>
@@ -5638,7 +5639,7 @@
       </c>
       <c r="M168"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13">
       <c r="A169">
         <v>88</v>
       </c>
@@ -5661,7 +5662,7 @@
       </c>
       <c r="M169"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13">
       <c r="A170">
         <v>91</v>
       </c>
@@ -5686,7 +5687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13">
       <c r="A171">
         <v>94</v>
       </c>
@@ -5711,7 +5712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13">
       <c r="A172">
         <v>94</v>
       </c>
@@ -5734,7 +5735,7 @@
       </c>
       <c r="M172"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13">
       <c r="A173">
         <v>94</v>
       </c>
@@ -5759,7 +5760,7 @@
       </c>
       <c r="M173"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13">
       <c r="A174">
         <v>94</v>
       </c>
@@ -5784,7 +5785,7 @@
       </c>
       <c r="M174"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13">
       <c r="A175">
         <v>94</v>
       </c>
@@ -5809,7 +5810,7 @@
       </c>
       <c r="M175"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13">
       <c r="A176">
         <v>95</v>
       </c>
@@ -5834,7 +5835,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13">
       <c r="A177">
         <v>95</v>
       </c>
@@ -5859,7 +5860,7 @@
       </c>
       <c r="M177"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13">
       <c r="A178">
         <v>96</v>
       </c>
@@ -5884,7 +5885,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13">
       <c r="A179">
         <v>96</v>
       </c>
@@ -5909,7 +5910,7 @@
       </c>
       <c r="M179"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13">
       <c r="A180">
         <v>97</v>
       </c>
@@ -5934,7 +5935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13">
       <c r="A181">
         <v>98</v>
       </c>
@@ -5959,7 +5960,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13">
       <c r="A182">
         <v>99</v>
       </c>
@@ -5984,7 +5985,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13">
       <c r="A183">
         <v>100</v>
       </c>
@@ -6009,7 +6010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13">
       <c r="A184">
         <v>101</v>
       </c>
@@ -6034,7 +6035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13">
       <c r="A185">
         <v>102</v>
       </c>
@@ -6059,7 +6060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13">
       <c r="A186">
         <v>103</v>
       </c>
@@ -6084,7 +6085,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13">
       <c r="A187">
         <v>103</v>
       </c>
@@ -6109,7 +6110,7 @@
       </c>
       <c r="M187"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13">
       <c r="A188">
         <v>104</v>
       </c>
@@ -6134,7 +6135,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13">
       <c r="A189">
         <v>104</v>
       </c>
@@ -6159,7 +6160,7 @@
       </c>
       <c r="M189"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13">
       <c r="A190">
         <v>104</v>
       </c>
@@ -6184,7 +6185,7 @@
       </c>
       <c r="M190"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13">
       <c r="A191">
         <v>105</v>
       </c>
@@ -6209,7 +6210,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13">
       <c r="A192">
         <v>106</v>
       </c>
@@ -6234,7 +6235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13">
       <c r="A193">
         <v>107</v>
       </c>
@@ -6259,7 +6260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13">
       <c r="A194">
         <v>107</v>
       </c>
@@ -6284,7 +6285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13">
       <c r="A195">
         <v>107</v>
       </c>
@@ -6309,7 +6310,7 @@
       </c>
       <c r="M195"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13">
       <c r="A196">
         <v>107</v>
       </c>
@@ -6334,7 +6335,7 @@
       </c>
       <c r="M196"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13">
       <c r="A197">
         <v>108</v>
       </c>
@@ -6359,7 +6360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13">
       <c r="A198">
         <v>109</v>
       </c>
@@ -6384,7 +6385,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13">
       <c r="A199">
         <v>109</v>
       </c>
@@ -6409,7 +6410,7 @@
       </c>
       <c r="M199"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13">
       <c r="A200">
         <v>109</v>
       </c>
@@ -6434,7 +6435,7 @@
       </c>
       <c r="M200"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13">
       <c r="A201">
         <v>110</v>
       </c>
@@ -6459,7 +6460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13">
       <c r="A202">
         <v>111</v>
       </c>
@@ -6484,7 +6485,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13">
       <c r="A203">
         <v>112</v>
       </c>
@@ -6509,7 +6510,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13">
       <c r="A204">
         <v>113</v>
       </c>
@@ -6534,7 +6535,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13">
       <c r="A205">
         <v>114</v>
       </c>
@@ -6559,7 +6560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13">
       <c r="A206">
         <v>115</v>
       </c>
@@ -6584,7 +6585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13">
       <c r="A207">
         <v>116</v>
       </c>
@@ -6609,7 +6610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13">
       <c r="A208">
         <v>117</v>
       </c>
@@ -6634,7 +6635,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13">
       <c r="A209">
         <v>118</v>
       </c>
@@ -6659,7 +6660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13">
       <c r="A210">
         <v>118</v>
       </c>
@@ -6684,7 +6685,7 @@
       </c>
       <c r="M210"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13">
       <c r="A211">
         <v>118</v>
       </c>
@@ -6709,7 +6710,7 @@
       </c>
       <c r="M211"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13">
       <c r="A212">
         <v>119</v>
       </c>
@@ -6734,7 +6735,7 @@
       </c>
       <c r="M212"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13">
       <c r="A213">
         <v>119</v>
       </c>
@@ -6759,7 +6760,7 @@
       </c>
       <c r="M213"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13">
       <c r="A214">
         <v>120</v>
       </c>
@@ -6786,7 +6787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13">
       <c r="A215">
         <v>121</v>
       </c>
@@ -6811,7 +6812,7 @@
       </c>
       <c r="M215"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13">
       <c r="A216">
         <v>121</v>
       </c>
@@ -6836,7 +6837,7 @@
       </c>
       <c r="M216"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13">
       <c r="A217">
         <v>122</v>
       </c>
@@ -6861,7 +6862,7 @@
       </c>
       <c r="M217"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13">
       <c r="A218">
         <v>123</v>
       </c>
@@ -6886,7 +6887,7 @@
       </c>
       <c r="M218"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13">
       <c r="A219">
         <v>124</v>
       </c>
@@ -6911,7 +6912,7 @@
       </c>
       <c r="M219"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13">
       <c r="A220">
         <v>125</v>
       </c>
@@ -6936,7 +6937,7 @@
       </c>
       <c r="M220"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13">
       <c r="A221">
         <v>126</v>
       </c>
@@ -6965,7 +6966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13">
       <c r="A222">
         <v>127</v>
       </c>
@@ -6990,7 +6991,7 @@
       </c>
       <c r="M222"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13">
       <c r="A223">
         <v>127</v>
       </c>
@@ -7015,7 +7016,7 @@
       </c>
       <c r="M223"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13">
       <c r="A224">
         <v>127</v>
       </c>
@@ -7040,7 +7041,7 @@
       </c>
       <c r="M224"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13">
       <c r="A225">
         <v>127</v>
       </c>
@@ -7067,7 +7068,7 @@
       </c>
       <c r="M225"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13">
       <c r="A226">
         <v>127</v>
       </c>
@@ -7094,7 +7095,7 @@
       </c>
       <c r="M226"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13">
       <c r="A227">
         <v>128</v>
       </c>
@@ -7121,7 +7122,7 @@
       </c>
       <c r="M227"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13">
       <c r="A228">
         <v>129</v>
       </c>
@@ -7150,7 +7151,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13">
       <c r="A229">
         <v>129</v>
       </c>
@@ -7175,7 +7176,7 @@
       </c>
       <c r="M229"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13">
       <c r="A230">
         <v>130</v>
       </c>
@@ -7202,7 +7203,7 @@
       </c>
       <c r="M230"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13">
       <c r="A231">
         <v>130</v>
       </c>
@@ -7227,7 +7228,7 @@
       </c>
       <c r="M231"/>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13">
       <c r="A232">
         <v>131</v>
       </c>
@@ -7252,7 +7253,7 @@
       </c>
       <c r="M232"/>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13">
       <c r="A233">
         <v>131</v>
       </c>
@@ -7277,7 +7278,7 @@
       </c>
       <c r="M233"/>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13">
       <c r="A234">
         <v>131</v>
       </c>
@@ -7302,7 +7303,7 @@
       </c>
       <c r="M234"/>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13">
       <c r="A235">
         <v>131</v>
       </c>
@@ -7327,7 +7328,7 @@
       </c>
       <c r="M235"/>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13">
       <c r="A236">
         <v>131</v>
       </c>
@@ -7352,7 +7353,7 @@
       </c>
       <c r="M236"/>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13">
       <c r="A237">
         <v>131</v>
       </c>
@@ -7377,7 +7378,7 @@
       </c>
       <c r="M237"/>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13">
       <c r="A238">
         <v>132</v>
       </c>
@@ -7402,7 +7403,7 @@
       </c>
       <c r="M238"/>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13">
       <c r="A239">
         <v>133</v>
       </c>
@@ -7427,7 +7428,7 @@
       </c>
       <c r="M239"/>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13">
       <c r="A240">
         <v>134</v>
       </c>
@@ -7452,7 +7453,7 @@
       </c>
       <c r="M240"/>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13">
       <c r="A241">
         <v>135</v>
       </c>
@@ -7477,7 +7478,7 @@
       </c>
       <c r="M241"/>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13">
       <c r="A242">
         <v>136</v>
       </c>
@@ -7504,7 +7505,7 @@
       </c>
       <c r="M242"/>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13">
       <c r="A243">
         <v>137</v>
       </c>
@@ -7529,7 +7530,7 @@
       </c>
       <c r="M243"/>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13">
       <c r="A244">
         <v>138</v>
       </c>
@@ -7554,7 +7555,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13">
       <c r="A245">
         <v>139</v>
       </c>
@@ -7579,7 +7580,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13">
       <c r="A246">
         <v>140</v>
       </c>
@@ -7604,7 +7605,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13">
       <c r="A247">
         <v>141</v>
       </c>
@@ -7629,7 +7630,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13">
       <c r="A248">
         <v>142</v>
       </c>
@@ -7654,7 +7655,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13">
       <c r="A249">
         <v>143</v>
       </c>
@@ -7679,7 +7680,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13">
       <c r="A250">
         <v>144</v>
       </c>
@@ -7710,7 +7711,7 @@
       </c>
       <c r="M250"/>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13">
       <c r="A251">
         <v>145</v>
       </c>
@@ -7737,7 +7738,7 @@
       </c>
       <c r="M251"/>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13">
       <c r="A252">
         <v>146</v>
       </c>
@@ -7764,7 +7765,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13">
       <c r="A253">
         <v>147</v>
       </c>
@@ -7789,7 +7790,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13">
       <c r="A254">
         <v>149</v>
       </c>
@@ -7812,7 +7813,7 @@
       </c>
       <c r="M254"/>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13">
       <c r="A255">
         <v>149</v>
       </c>
@@ -7835,7 +7836,7 @@
       </c>
       <c r="M255"/>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13">
       <c r="A256">
         <v>150</v>
       </c>
@@ -7862,7 +7863,7 @@
       </c>
       <c r="M256"/>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13">
       <c r="A257">
         <v>150</v>
       </c>
@@ -7889,7 +7890,7 @@
       </c>
       <c r="M257"/>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13">
       <c r="A258">
         <v>150</v>
       </c>
@@ -7916,7 +7917,7 @@
       </c>
       <c r="M258"/>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13">
       <c r="A259">
         <v>151</v>
       </c>
@@ -7945,7 +7946,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13">
       <c r="A260">
         <v>151</v>
       </c>
@@ -7974,7 +7975,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13">
       <c r="A261">
         <v>151</v>
       </c>
@@ -8001,7 +8002,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13">
       <c r="A262">
         <v>151</v>
       </c>
@@ -8030,7 +8031,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13">
       <c r="A263">
         <v>151</v>
       </c>
@@ -8057,7 +8058,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13">
       <c r="A264">
         <v>151</v>
       </c>
@@ -8084,7 +8085,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13">
       <c r="A265">
         <v>151</v>
       </c>
@@ -8113,7 +8114,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13">
       <c r="A266">
         <v>152</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13">
       <c r="A267">
         <v>152</v>
       </c>
@@ -8169,7 +8170,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13">
       <c r="A268">
         <v>153</v>
       </c>
@@ -8198,7 +8199,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13">
       <c r="A269">
         <v>153</v>
       </c>
@@ -8227,7 +8228,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13">
       <c r="A270">
         <v>153</v>
       </c>
@@ -8254,7 +8255,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13">
       <c r="A271">
         <v>153</v>
       </c>
@@ -8281,7 +8282,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13">
       <c r="A272">
         <v>154</v>
       </c>
@@ -8308,7 +8309,7 @@
       </c>
       <c r="M272"/>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13">
       <c r="A273">
         <v>155</v>
       </c>
@@ -8335,7 +8336,7 @@
       </c>
       <c r="M273"/>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13">
       <c r="A274">
         <v>156</v>
       </c>
@@ -8362,7 +8363,7 @@
       </c>
       <c r="M274"/>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13">
       <c r="A275">
         <v>156</v>
       </c>
@@ -8389,7 +8390,7 @@
       </c>
       <c r="M275"/>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13">
       <c r="A276">
         <v>157</v>
       </c>
@@ -8412,7 +8413,7 @@
       </c>
       <c r="M276"/>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13">
       <c r="A277">
         <v>158</v>
       </c>
@@ -8435,7 +8436,7 @@
       </c>
       <c r="M277"/>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13">
       <c r="A278">
         <v>159</v>
       </c>
@@ -8458,7 +8459,7 @@
       </c>
       <c r="M278"/>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13">
       <c r="A279">
         <v>160</v>
       </c>
@@ -8485,7 +8486,7 @@
       </c>
       <c r="M279"/>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13">
       <c r="A280">
         <v>161</v>
       </c>
@@ -8514,7 +8515,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13">
       <c r="A281">
         <v>161</v>
       </c>
@@ -8541,7 +8542,7 @@
       </c>
       <c r="M281"/>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13">
       <c r="A282">
         <v>161</v>
       </c>
@@ -8568,7 +8569,7 @@
       </c>
       <c r="M282"/>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13">
       <c r="A283">
         <v>162</v>
       </c>
@@ -8593,7 +8594,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13">
       <c r="A284">
         <v>163</v>
       </c>
@@ -8620,7 +8621,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13">
       <c r="A285">
         <v>164</v>
       </c>
@@ -8645,7 +8646,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13">
       <c r="A286">
         <v>165</v>
       </c>
@@ -8670,7 +8671,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13">
       <c r="A287">
         <v>166</v>
       </c>
@@ -8697,7 +8698,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13">
       <c r="A288">
         <v>167</v>
       </c>
@@ -8724,7 +8725,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13">
       <c r="A289">
         <v>168</v>
       </c>
@@ -8749,7 +8750,7 @@
       </c>
       <c r="M289"/>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13">
       <c r="A290">
         <v>169</v>
       </c>
@@ -8774,7 +8775,7 @@
       </c>
       <c r="M290"/>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13">
       <c r="A291">
         <v>170</v>
       </c>
@@ -8797,7 +8798,7 @@
       </c>
       <c r="M291"/>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13">
       <c r="A292">
         <v>171</v>
       </c>
@@ -8822,7 +8823,7 @@
       </c>
       <c r="M292"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13">
       <c r="A293">
         <v>172</v>
       </c>
@@ -8851,7 +8852,7 @@
       </c>
       <c r="M293"/>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13">
       <c r="A294">
         <v>172</v>
       </c>
@@ -8882,7 +8883,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13">
       <c r="A295">
         <v>172</v>
       </c>
@@ -8911,7 +8912,7 @@
       </c>
       <c r="M295"/>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13">
       <c r="A296">
         <v>172</v>
       </c>
@@ -8942,7 +8943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13">
       <c r="A297">
         <v>172</v>
       </c>
@@ -8971,7 +8972,7 @@
       </c>
       <c r="M297"/>
     </row>
-    <row r="298" spans="1:13" ht="23.25" x14ac:dyDescent="0.6">
+    <row r="298" spans="1:13">
       <c r="A298">
         <v>172</v>
       </c>
@@ -9000,7 +9001,7 @@
       </c>
       <c r="M298"/>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13">
       <c r="A299">
         <v>172</v>
       </c>
@@ -9029,7 +9030,7 @@
       </c>
       <c r="M299"/>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13">
       <c r="A300">
         <v>172</v>
       </c>
@@ -9058,7 +9059,7 @@
       </c>
       <c r="M300"/>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13">
       <c r="A301">
         <v>172</v>
       </c>
@@ -9083,7 +9084,7 @@
       </c>
       <c r="M301"/>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13">
       <c r="A302">
         <v>173</v>
       </c>
@@ -9112,7 +9113,7 @@
       </c>
       <c r="M302"/>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13">
       <c r="A303">
         <v>173</v>
       </c>
@@ -9139,7 +9140,7 @@
       </c>
       <c r="M303"/>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13">
       <c r="A304">
         <v>173</v>
       </c>
@@ -9164,7 +9165,7 @@
       </c>
       <c r="M304"/>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13">
       <c r="A305">
         <v>174</v>
       </c>
@@ -9191,7 +9192,7 @@
       </c>
       <c r="M305"/>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13">
       <c r="A306">
         <v>175</v>
       </c>
@@ -9218,7 +9219,7 @@
       </c>
       <c r="M306"/>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13">
       <c r="A307">
         <v>175</v>
       </c>
@@ -9245,7 +9246,7 @@
       </c>
       <c r="M307"/>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13">
       <c r="A308">
         <v>175</v>
       </c>
@@ -9272,7 +9273,7 @@
       </c>
       <c r="M308"/>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13">
       <c r="A309">
         <v>175</v>
       </c>
@@ -9301,7 +9302,7 @@
       </c>
       <c r="M309"/>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13">
       <c r="A310">
         <v>176</v>
       </c>
@@ -9328,7 +9329,7 @@
       </c>
       <c r="M310"/>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13">
       <c r="A311">
         <v>177</v>
       </c>
@@ -9355,7 +9356,7 @@
       </c>
       <c r="M311"/>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13">
       <c r="A312">
         <v>178</v>
       </c>
@@ -9384,7 +9385,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13">
       <c r="A313">
         <v>178</v>
       </c>
@@ -9413,7 +9414,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13">
       <c r="A314">
         <v>179</v>
       </c>
@@ -9440,7 +9441,7 @@
       </c>
       <c r="M314"/>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13">
       <c r="A315">
         <v>180</v>
       </c>
@@ -9465,7 +9466,7 @@
       </c>
       <c r="M315"/>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13">
       <c r="A316">
         <v>181</v>
       </c>
@@ -9492,7 +9493,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13">
       <c r="A317">
         <v>182</v>
       </c>
@@ -9519,7 +9520,7 @@
       </c>
       <c r="M317"/>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13">
       <c r="A318">
         <v>216</v>
       </c>
@@ -9548,7 +9549,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13">
       <c r="A319">
         <v>216</v>
       </c>
@@ -9577,7 +9578,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13">
       <c r="A320">
         <v>216</v>
       </c>
@@ -9604,7 +9605,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13">
       <c r="A321">
         <v>216</v>
       </c>
@@ -9631,7 +9632,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13">
       <c r="A322">
         <v>216</v>
       </c>
@@ -9658,7 +9659,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13">
       <c r="A323">
         <v>216</v>
       </c>
@@ -9685,7 +9686,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13">
       <c r="A324">
         <v>216</v>
       </c>
@@ -9712,7 +9713,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13">
       <c r="A325">
         <v>216</v>
       </c>
@@ -9739,7 +9740,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13">
       <c r="A326">
         <v>216</v>
       </c>
@@ -9766,7 +9767,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13">
       <c r="A327">
         <v>184</v>
       </c>
@@ -9793,7 +9794,7 @@
       </c>
       <c r="M327"/>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13">
       <c r="A328">
         <v>185</v>
       </c>
@@ -9820,7 +9821,7 @@
       </c>
       <c r="M328"/>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13">
       <c r="A329">
         <v>185</v>
       </c>
@@ -9847,7 +9848,7 @@
       </c>
       <c r="M329"/>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13">
       <c r="A330">
         <v>186</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13">
       <c r="A331">
         <v>186</v>
       </c>
@@ -9919,7 +9920,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13">
       <c r="A332">
         <v>186</v>
       </c>
@@ -9952,7 +9953,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13">
       <c r="A333">
         <v>186</v>
       </c>
@@ -9987,7 +9988,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13">
       <c r="A334">
         <v>187</v>
       </c>
@@ -10014,7 +10015,7 @@
       </c>
       <c r="M334"/>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13">
       <c r="A335">
         <v>187</v>
       </c>
@@ -10039,7 +10040,7 @@
       </c>
       <c r="M335"/>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13">
       <c r="A336">
         <v>187</v>
       </c>
@@ -10066,7 +10067,7 @@
       </c>
       <c r="M336"/>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13">
       <c r="A337">
         <v>188</v>
       </c>
@@ -10093,7 +10094,7 @@
       </c>
       <c r="M337"/>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13">
       <c r="A338">
         <v>189</v>
       </c>
@@ -10122,7 +10123,7 @@
       </c>
       <c r="M338"/>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13">
       <c r="A339">
         <v>189</v>
       </c>
@@ -10149,7 +10150,7 @@
       </c>
       <c r="M339"/>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13">
       <c r="A340">
         <v>189</v>
       </c>
@@ -10176,7 +10177,7 @@
       </c>
       <c r="M340"/>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13">
       <c r="A341">
         <v>190</v>
       </c>
@@ -10205,7 +10206,7 @@
       </c>
       <c r="M341"/>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13">
       <c r="A342">
         <v>191</v>
       </c>
@@ -10234,7 +10235,7 @@
       </c>
       <c r="M342"/>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13">
       <c r="A343">
         <v>192</v>
       </c>
@@ -10261,7 +10262,7 @@
       </c>
       <c r="M343"/>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13">
       <c r="A344">
         <v>193</v>
       </c>
@@ -10290,7 +10291,7 @@
       </c>
       <c r="M344"/>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13">
       <c r="A345">
         <v>193</v>
       </c>
@@ -10319,7 +10320,7 @@
       </c>
       <c r="M345"/>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13">
       <c r="A346">
         <v>193</v>
       </c>
@@ -10346,7 +10347,7 @@
       </c>
       <c r="M346"/>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13">
       <c r="A347">
         <v>193</v>
       </c>
@@ -10373,7 +10374,7 @@
       </c>
       <c r="M347"/>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13">
       <c r="A348">
         <v>194</v>
       </c>
@@ -10404,7 +10405,7 @@
       </c>
       <c r="M348"/>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13">
       <c r="A349">
         <v>195</v>
       </c>
@@ -10431,7 +10432,7 @@
       </c>
       <c r="M349"/>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13">
       <c r="A350">
         <v>196</v>
       </c>
@@ -10460,7 +10461,7 @@
       </c>
       <c r="M350"/>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13">
       <c r="A351">
         <v>197</v>
       </c>
@@ -10487,7 +10488,7 @@
       </c>
       <c r="M351"/>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13">
       <c r="A352">
         <v>198</v>
       </c>
@@ -10514,7 +10515,7 @@
       </c>
       <c r="M352"/>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13">
       <c r="A353">
         <v>198</v>
       </c>
@@ -10539,7 +10540,7 @@
       </c>
       <c r="M353"/>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13">
       <c r="A354">
         <v>199</v>
       </c>
@@ -10566,7 +10567,7 @@
       </c>
       <c r="M354"/>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13">
       <c r="A355">
         <v>200</v>
       </c>
@@ -10591,7 +10592,7 @@
       </c>
       <c r="M355"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13">
       <c r="A356">
         <v>203</v>
       </c>
@@ -10618,7 +10619,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13">
       <c r="A357">
         <v>204</v>
       </c>
@@ -10645,7 +10646,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13">
       <c r="A358">
         <v>204</v>
       </c>
@@ -10672,7 +10673,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13">
       <c r="A359">
         <v>204</v>
       </c>
@@ -10699,7 +10700,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13">
       <c r="A360">
         <v>205</v>
       </c>
@@ -10726,7 +10727,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13">
       <c r="A361">
         <v>206</v>
       </c>
@@ -10751,7 +10752,7 @@
       </c>
       <c r="M361"/>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13">
       <c r="A362">
         <v>206</v>
       </c>
@@ -10776,7 +10777,7 @@
       </c>
       <c r="M362"/>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13">
       <c r="A363">
         <v>207</v>
       </c>
@@ -10801,7 +10802,7 @@
       </c>
       <c r="M363"/>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13">
       <c r="A364">
         <v>209</v>
       </c>
@@ -10826,7 +10827,7 @@
       </c>
       <c r="M364"/>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13">
       <c r="A365">
         <v>210</v>
       </c>
@@ -10851,7 +10852,7 @@
       </c>
       <c r="M365"/>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13">
       <c r="A366">
         <v>211</v>
       </c>
@@ -10876,7 +10877,7 @@
       </c>
       <c r="M366"/>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13">
       <c r="A367">
         <v>211</v>
       </c>
@@ -10901,7 +10902,7 @@
       </c>
       <c r="M367"/>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13">
       <c r="A368">
         <v>211</v>
       </c>
@@ -10926,7 +10927,7 @@
       </c>
       <c r="M368"/>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13">
       <c r="A369">
         <v>212</v>
       </c>
@@ -10953,7 +10954,7 @@
       </c>
       <c r="M369"/>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13">
       <c r="A370">
         <v>213</v>
       </c>
@@ -10980,7 +10981,7 @@
       </c>
       <c r="M370"/>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13">
       <c r="A371">
         <v>214</v>
       </c>
@@ -11005,7 +11006,7 @@
       </c>
       <c r="M371"/>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13">
       <c r="A372">
         <v>214</v>
       </c>
@@ -11030,7 +11031,7 @@
       </c>
       <c r="M372"/>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13">
       <c r="A373">
         <v>215</v>
       </c>
@@ -11055,7 +11056,7 @@
       </c>
       <c r="M373"/>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13">
       <c r="A374">
         <v>217</v>
       </c>
@@ -11080,7 +11081,7 @@
       </c>
       <c r="M374"/>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13">
       <c r="A375">
         <v>218</v>
       </c>

--- a/db/data/office_transactions.xlsx
+++ b/db/data/office_transactions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004DB22F-C754-4190-9451-60869542A4FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339535A-25A1-4EEA-B711-36A825809BB2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="265">
   <si>
     <t xml:space="preserve">पुरानो </t>
   </si>
@@ -532,9 +532,6 @@
   </si>
   <si>
     <t>2070-09-16</t>
-  </si>
-  <si>
-    <t>०२. 47</t>
   </si>
   <si>
     <t>2071-03-23</t>
@@ -974,7 +971,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1026,7 +1023,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1249,43 +1246,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" t="s">
         <v>252</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>253</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>254</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>255</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>256</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>257</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>258</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>259</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>260</v>
-      </c>
-      <c r="M1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -3273,7 +3270,7 @@
         <v>35</v>
       </c>
       <c r="B76" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C76"/>
       <c r="D76"/>
@@ -3902,7 +3899,7 @@
         <v>50</v>
       </c>
       <c r="B101" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C101">
         <v>92</v>
@@ -3931,7 +3928,7 @@
         <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C102">
         <v>130</v>
@@ -3960,7 +3957,7 @@
         <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C103">
         <v>135</v>
@@ -4045,7 +4042,7 @@
         <v>50</v>
       </c>
       <c r="B106" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C106">
         <v>16</v>
@@ -4074,7 +4071,7 @@
         <v>50</v>
       </c>
       <c r="B107" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C107">
         <v>19</v>
@@ -4190,7 +4187,7 @@
         <v>50</v>
       </c>
       <c r="B111" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C111">
         <v>67</v>
@@ -6532,7 +6529,7 @@
         <v>346</v>
       </c>
       <c r="M204" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -7685,7 +7682,7 @@
         <v>144</v>
       </c>
       <c r="B250" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C250">
         <v>18</v>
@@ -8252,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="M270" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="271" spans="1:13">
@@ -8834,7 +8831,7 @@
         <v>94</v>
       </c>
       <c r="D293" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E293"/>
       <c r="F293"/>
@@ -8857,13 +8854,13 @@
         <v>172</v>
       </c>
       <c r="B294" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C294">
         <v>72</v>
       </c>
       <c r="D294" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E294"/>
       <c r="F294"/>
@@ -8880,7 +8877,7 @@
         <v>84686</v>
       </c>
       <c r="M294" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="295" spans="1:13">
@@ -8888,13 +8885,13 @@
         <v>172</v>
       </c>
       <c r="B295" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C295">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E295"/>
       <c r="F295"/>
@@ -8917,13 +8914,13 @@
         <v>172</v>
       </c>
       <c r="B296" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C296">
         <v>55</v>
       </c>
       <c r="D296" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E296"/>
       <c r="F296"/>
@@ -8954,7 +8951,7 @@
         <v>55</v>
       </c>
       <c r="D297" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E297"/>
       <c r="F297"/>
@@ -8977,13 +8974,13 @@
         <v>172</v>
       </c>
       <c r="B298" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C298">
         <v>53</v>
       </c>
       <c r="D298" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E298"/>
       <c r="F298"/>
@@ -9006,13 +9003,13 @@
         <v>172</v>
       </c>
       <c r="B299" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C299">
         <v>53</v>
       </c>
       <c r="D299" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E299"/>
       <c r="F299"/>
@@ -9041,7 +9038,7 @@
         <v>37</v>
       </c>
       <c r="D300" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E300"/>
       <c r="F300"/>
@@ -9473,8 +9470,8 @@
       <c r="B316" t="s">
         <v>165</v>
       </c>
-      <c r="C316" t="s">
-        <v>166</v>
+      <c r="C316">
+        <v>47</v>
       </c>
       <c r="D316"/>
       <c r="E316"/>
@@ -9498,7 +9495,7 @@
         <v>182</v>
       </c>
       <c r="B317" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C317">
         <v>67</v>
@@ -9509,7 +9506,7 @@
       <c r="G317"/>
       <c r="H317"/>
       <c r="I317" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J317"/>
       <c r="K317">
@@ -9525,7 +9522,7 @@
         <v>216</v>
       </c>
       <c r="B318" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C318">
         <v>72</v>
@@ -9546,7 +9543,7 @@
         <v>214700</v>
       </c>
       <c r="M318" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="319" spans="1:13">
@@ -9554,7 +9551,7 @@
         <v>216</v>
       </c>
       <c r="B319" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C319">
         <v>35</v>
@@ -9575,7 +9572,7 @@
         <v>263800</v>
       </c>
       <c r="M319" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="320" spans="1:13">
@@ -9583,7 +9580,7 @@
         <v>216</v>
       </c>
       <c r="B320" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C320"/>
       <c r="D320"/>
@@ -9602,7 +9599,7 @@
         <v>175900</v>
       </c>
       <c r="M320" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="321" spans="1:13">
@@ -9610,7 +9607,7 @@
         <v>216</v>
       </c>
       <c r="B321" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C321"/>
       <c r="D321"/>
@@ -9629,7 +9626,7 @@
         <v>1950000</v>
       </c>
       <c r="M321" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="322" spans="1:13">
@@ -9637,7 +9634,7 @@
         <v>216</v>
       </c>
       <c r="B322" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C322"/>
       <c r="D322"/>
@@ -9656,7 +9653,7 @@
         <v>265400</v>
       </c>
       <c r="M322" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="323" spans="1:13">
@@ -9664,7 +9661,7 @@
         <v>216</v>
       </c>
       <c r="B323" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C323"/>
       <c r="D323"/>
@@ -9683,7 +9680,7 @@
         <v>114000</v>
       </c>
       <c r="M323" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="324" spans="1:13">
@@ -9691,7 +9688,7 @@
         <v>216</v>
       </c>
       <c r="B324" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C324"/>
       <c r="D324"/>
@@ -9710,7 +9707,7 @@
         <v>263900</v>
       </c>
       <c r="M324" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="325" spans="1:13">
@@ -9718,7 +9715,7 @@
         <v>216</v>
       </c>
       <c r="B325" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C325"/>
       <c r="D325"/>
@@ -9737,7 +9734,7 @@
         <v>265400</v>
       </c>
       <c r="M325" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="326" spans="1:13">
@@ -9745,7 +9742,7 @@
         <v>216</v>
       </c>
       <c r="B326" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C326"/>
       <c r="D326"/>
@@ -9764,7 +9761,7 @@
         <v>264500</v>
       </c>
       <c r="M326" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="327" spans="1:13">
@@ -9772,7 +9769,7 @@
         <v>184</v>
       </c>
       <c r="B327" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C327">
         <v>77</v>
@@ -9799,7 +9796,7 @@
         <v>185</v>
       </c>
       <c r="B328" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C328">
         <v>78</v>
@@ -9853,26 +9850,26 @@
         <v>186</v>
       </c>
       <c r="B330" t="s">
+        <v>182</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+      <c r="D330" t="s">
+        <v>185</v>
+      </c>
+      <c r="E330" t="s">
+        <v>186</v>
+      </c>
+      <c r="F330" t="s">
+        <v>184</v>
+      </c>
+      <c r="G330" t="s">
         <v>183</v>
-      </c>
-      <c r="C330">
-        <v>1</v>
-      </c>
-      <c r="D330" t="s">
-        <v>186</v>
-      </c>
-      <c r="E330" t="s">
-        <v>187</v>
-      </c>
-      <c r="F330" t="s">
-        <v>185</v>
-      </c>
-      <c r="G330" t="s">
-        <v>184</v>
       </c>
       <c r="H330"/>
       <c r="I330" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J330"/>
       <c r="K330">
@@ -9882,7 +9879,7 @@
         <v>93750</v>
       </c>
       <c r="M330" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="331" spans="1:13">
@@ -9896,18 +9893,18 @@
         <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E331" t="s">
+        <v>195</v>
+      </c>
+      <c r="F331" t="s">
         <v>196</v>
-      </c>
-      <c r="F331" t="s">
-        <v>197</v>
       </c>
       <c r="G331"/>
       <c r="H331"/>
       <c r="I331" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J331"/>
       <c r="K331">
@@ -9925,22 +9922,22 @@
         <v>186</v>
       </c>
       <c r="B332" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C332">
         <v>1</v>
       </c>
       <c r="D332"/>
       <c r="E332" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F332" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G332"/>
       <c r="H332"/>
       <c r="I332" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J332"/>
       <c r="K332">
@@ -9958,24 +9955,24 @@
         <v>186</v>
       </c>
       <c r="B333" t="s">
+        <v>189</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+      <c r="D333" t="s">
         <v>190</v>
       </c>
-      <c r="C333">
-        <v>1</v>
-      </c>
-      <c r="D333" t="s">
-        <v>191</v>
-      </c>
       <c r="E333" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F333" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G333"/>
       <c r="H333"/>
       <c r="I333" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J333"/>
       <c r="K333">
@@ -9985,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="M333" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="334" spans="1:13">
@@ -9993,7 +9990,7 @@
         <v>187</v>
       </c>
       <c r="B334" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10020,7 +10017,7 @@
         <v>187</v>
       </c>
       <c r="B335" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C335">
         <v>9</v>
@@ -10045,7 +10042,7 @@
         <v>187</v>
       </c>
       <c r="B336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C336">
         <v>22</v>
@@ -10072,7 +10069,7 @@
         <v>188</v>
       </c>
       <c r="B337" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C337">
         <v>55</v>
@@ -10099,7 +10096,7 @@
         <v>189</v>
       </c>
       <c r="B338" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C338">
         <v>55</v>
@@ -10107,7 +10104,7 @@
       <c r="D338"/>
       <c r="E338"/>
       <c r="F338" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G338"/>
       <c r="H338"/>
@@ -10136,7 +10133,7 @@
       <c r="D339"/>
       <c r="E339"/>
       <c r="F339" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G339"/>
       <c r="H339"/>
@@ -10155,7 +10152,7 @@
         <v>189</v>
       </c>
       <c r="B340" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10182,7 +10179,7 @@
         <v>190</v>
       </c>
       <c r="B341" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C341">
         <v>56</v>
@@ -10196,7 +10193,7 @@
         <v>132</v>
       </c>
       <c r="J341" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K341">
         <v>1</v>
@@ -10217,14 +10214,14 @@
         <v>64</v>
       </c>
       <c r="D342" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E342"/>
       <c r="F342"/>
       <c r="G342"/>
       <c r="H342"/>
       <c r="I342" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J342"/>
       <c r="K342">
@@ -10240,7 +10237,7 @@
         <v>192</v>
       </c>
       <c r="B343" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C343">
         <v>79</v>
@@ -10267,7 +10264,7 @@
         <v>193</v>
       </c>
       <c r="B344" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C344">
         <v>79</v>
@@ -10275,12 +10272,12 @@
       <c r="D344"/>
       <c r="E344"/>
       <c r="F344" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G344"/>
       <c r="H344"/>
       <c r="I344" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J344"/>
       <c r="K344">
@@ -10296,20 +10293,20 @@
         <v>193</v>
       </c>
       <c r="B345" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C345"/>
       <c r="D345"/>
       <c r="E345"/>
       <c r="F345" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G345" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H345"/>
       <c r="I345" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J345"/>
       <c r="K345">
@@ -10325,7 +10322,7 @@
         <v>193</v>
       </c>
       <c r="B346" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C346"/>
       <c r="D346"/>
@@ -10334,10 +10331,10 @@
       <c r="G346"/>
       <c r="H346"/>
       <c r="I346" t="s">
+        <v>212</v>
+      </c>
+      <c r="J346" t="s">
         <v>213</v>
-      </c>
-      <c r="J346" t="s">
-        <v>214</v>
       </c>
       <c r="K346">
         <v>1</v>
@@ -10363,7 +10360,7 @@
       <c r="G347"/>
       <c r="H347"/>
       <c r="I347" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J347"/>
       <c r="K347">
@@ -10387,14 +10384,14 @@
       <c r="D348"/>
       <c r="E348"/>
       <c r="F348" t="s">
+        <v>214</v>
+      </c>
+      <c r="G348" t="s">
         <v>215</v>
-      </c>
-      <c r="G348" t="s">
-        <v>216</v>
       </c>
       <c r="H348"/>
       <c r="I348" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J348"/>
       <c r="K348">
@@ -10421,7 +10418,7 @@
       <c r="G349"/>
       <c r="H349"/>
       <c r="I349" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J349"/>
       <c r="K349">
@@ -10437,7 +10434,7 @@
         <v>196</v>
       </c>
       <c r="B350" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C350">
         <v>33</v>
@@ -10446,11 +10443,11 @@
       <c r="E350"/>
       <c r="F350"/>
       <c r="G350" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H350"/>
       <c r="I350" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J350"/>
       <c r="K350">
@@ -10466,7 +10463,7 @@
         <v>197</v>
       </c>
       <c r="B351" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C351">
         <v>33</v>
@@ -10477,7 +10474,7 @@
       <c r="G351"/>
       <c r="H351"/>
       <c r="I351" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J351"/>
       <c r="K351">
@@ -10493,7 +10490,7 @@
         <v>198</v>
       </c>
       <c r="B352" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C352">
         <v>49</v>
@@ -10504,7 +10501,7 @@
       <c r="G352"/>
       <c r="H352"/>
       <c r="I352" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J352"/>
       <c r="K352">
@@ -10529,7 +10526,7 @@
       <c r="G353"/>
       <c r="H353"/>
       <c r="I353" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J353"/>
       <c r="K353">
@@ -10556,7 +10553,7 @@
       <c r="G354"/>
       <c r="H354"/>
       <c r="I354" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J354"/>
       <c r="K354">
@@ -10581,7 +10578,7 @@
       <c r="G355"/>
       <c r="H355"/>
       <c r="I355" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J355"/>
       <c r="K355">
@@ -10606,7 +10603,7 @@
       <c r="G356"/>
       <c r="H356"/>
       <c r="I356" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J356"/>
       <c r="K356">
@@ -10616,7 +10613,7 @@
         <v>35000</v>
       </c>
       <c r="M356" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="357" spans="1:13">
@@ -10633,7 +10630,7 @@
       <c r="G357"/>
       <c r="H357"/>
       <c r="I357" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J357"/>
       <c r="K357">
@@ -10643,7 +10640,7 @@
         <v>21000</v>
       </c>
       <c r="M357" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="358" spans="1:13">
@@ -10660,7 +10657,7 @@
       <c r="G358"/>
       <c r="H358"/>
       <c r="I358" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J358"/>
       <c r="K358">
@@ -10670,7 +10667,7 @@
         <v>28500</v>
       </c>
       <c r="M358" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="359" spans="1:13">
@@ -10687,7 +10684,7 @@
       <c r="G359"/>
       <c r="H359"/>
       <c r="I359" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J359"/>
       <c r="K359">
@@ -10697,7 +10694,7 @@
         <v>1850</v>
       </c>
       <c r="M359" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="360" spans="1:13">
@@ -10714,7 +10711,7 @@
       <c r="G360"/>
       <c r="H360"/>
       <c r="I360" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J360"/>
       <c r="K360">
@@ -10724,7 +10721,7 @@
         <v>20000</v>
       </c>
       <c r="M360" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="361" spans="1:13">
@@ -10857,7 +10854,7 @@
         <v>211</v>
       </c>
       <c r="B366" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C366">
         <v>37</v>
@@ -10882,7 +10879,7 @@
         <v>211</v>
       </c>
       <c r="B367" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C367">
         <v>5</v>
@@ -10907,7 +10904,7 @@
         <v>211</v>
       </c>
       <c r="B368" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C368">
         <v>24</v>
@@ -10932,7 +10929,7 @@
         <v>212</v>
       </c>
       <c r="B369" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C369">
         <v>38</v>
@@ -10943,7 +10940,7 @@
       <c r="G369"/>
       <c r="H369"/>
       <c r="I369" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J369"/>
       <c r="K369">
@@ -10959,7 +10956,7 @@
         <v>213</v>
       </c>
       <c r="B370" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C370">
         <v>52</v>
@@ -10970,7 +10967,7 @@
       <c r="G370"/>
       <c r="H370"/>
       <c r="I370" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J370"/>
       <c r="K370">
@@ -11061,7 +11058,7 @@
         <v>217</v>
       </c>
       <c r="B374" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C374">
         <v>21</v>
@@ -11086,7 +11083,7 @@
         <v>218</v>
       </c>
       <c r="B375" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C375">
         <v>26</v>
@@ -11097,7 +11094,7 @@
       <c r="G375"/>
       <c r="H375"/>
       <c r="I375" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J375"/>
       <c r="K375">

--- a/db/data/office_transactions.xlsx
+++ b/db/data/office_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339535A-25A1-4EEA-B711-36A825809BB2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0179421-2A5C-4226-9626-3052B5C0988C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
